--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="19">
   <si>
     <t>update_name</t>
   </si>
@@ -38,94 +38,10 @@
     <t>update_date</t>
   </si>
   <si>
-    <t>未完待续</t>
+    <t>家宴</t>
   </si>
   <si>
     <t>剧本杀</t>
-  </si>
-  <si>
-    <t>2026-02-21</t>
-  </si>
-  <si>
-    <t>月光下的诅咒</t>
-  </si>
-  <si>
-    <t>牛鬼蛇神</t>
-  </si>
-  <si>
-    <t>崇山乐园</t>
-  </si>
-  <si>
-    <t>2026-02-22</t>
-  </si>
-  <si>
-    <t>季风吹过橘色的海</t>
-  </si>
-  <si>
-    <t>2026-02-23</t>
-  </si>
-  <si>
-    <t>雪乡连环杀人事件2</t>
-  </si>
-  <si>
-    <t>豆大点事物语</t>
-  </si>
-  <si>
-    <t>盒子先生的秘密商店</t>
-  </si>
-  <si>
-    <t>孤城</t>
-  </si>
-  <si>
-    <t>刀鞘</t>
-  </si>
-  <si>
-    <t>精神病院4</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>最后的晚餐</t>
-  </si>
-  <si>
-    <t>青白</t>
-  </si>
-  <si>
-    <t>蓝色大丽花</t>
-  </si>
-  <si>
-    <t>此时彼刻之人</t>
-  </si>
-  <si>
-    <t>我与我诀别</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>红豆</t>
-  </si>
-  <si>
-    <t>长安秘案录</t>
-  </si>
-  <si>
-    <t>小说</t>
-  </si>
-  <si>
-    <t>2026-02-26</t>
-  </si>
-  <si>
-    <t>亡瘾</t>
-  </si>
-  <si>
-    <t>豺狼的日子</t>
-  </si>
-  <si>
-    <t>剧集</t>
-  </si>
-  <si>
-    <t>家宴</t>
   </si>
   <si>
     <t>2026-02-27</t>
@@ -180,19 +96,13 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
@@ -671,148 +581,144 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1343,7 +1249,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
@@ -1362,7 +1268,7 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
@@ -1384,7 +1290,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" t="s">
+      <c r="A4" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B4" t="s">
@@ -1395,344 +1301,124 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>10</v>
+      <c r="A6" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>12</v>
+      <c r="A7" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>4</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>13</v>
+      <c r="A8" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>14</v>
+      <c r="A9" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="B9" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="10" ht="15" spans="1:3">
+    <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="11" ht="15" spans="1:3">
+    <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
         <v>4</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="3" t="s">
-        <v>17</v>
+      <c r="A12" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="B12" t="s">
         <v>4</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>19</v>
+      <c r="A13" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="B13" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="3" t="s">
-        <v>20</v>
+      <c r="A14" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="B14" t="s">
         <v>4</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="3" t="s">
-        <v>21</v>
+      <c r="A15" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="B15" t="s">
         <v>4</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" ht="15" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" t="s">
-        <v>4</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" ht="15" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21" t="s">
-        <v>31</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" t="s">
-        <v>4</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
-        <v>34</v>
-      </c>
-      <c r="B23" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" t="s">
-        <v>4</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" t="s">
-        <v>4</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" t="s">
-        <v>4</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" t="s">
-        <v>4</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" t="s">
-        <v>4</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" t="s">
-        <v>4</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" t="s">
-        <v>4</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" t="s">
-        <v>4</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B33" t="s">
-        <v>4</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B34" t="s">
-        <v>4</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B35" t="s">
-        <v>4</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="47">
   <si>
     <t>update_name</t>
   </si>
@@ -38,10 +38,94 @@
     <t>update_date</t>
   </si>
   <si>
+    <t>未完待续</t>
+  </si>
+  <si>
+    <t>剧本杀</t>
+  </si>
+  <si>
+    <t>2026-02-21</t>
+  </si>
+  <si>
+    <t>月光下的诅咒</t>
+  </si>
+  <si>
+    <t>牛鬼蛇神</t>
+  </si>
+  <si>
+    <t>崇山乐园</t>
+  </si>
+  <si>
+    <t>2026-02-22</t>
+  </si>
+  <si>
+    <t>季风吹过橘色的海</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>雪乡连环杀人事件2</t>
+  </si>
+  <si>
+    <t>豆大点事物语</t>
+  </si>
+  <si>
+    <t>盒子先生的秘密商店</t>
+  </si>
+  <si>
+    <t>孤城</t>
+  </si>
+  <si>
+    <t>刀鞘</t>
+  </si>
+  <si>
+    <t>精神病院4</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>最后的晚餐</t>
+  </si>
+  <si>
+    <t>青白</t>
+  </si>
+  <si>
+    <t>蓝色大丽花</t>
+  </si>
+  <si>
+    <t>此时彼刻之人</t>
+  </si>
+  <si>
+    <t>我与我诀别</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>红豆</t>
+  </si>
+  <si>
+    <t>长安秘案录</t>
+  </si>
+  <si>
+    <t>小说</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>亡瘾</t>
+  </si>
+  <si>
+    <t>豺狼的日子</t>
+  </si>
+  <si>
+    <t>剧集</t>
+  </si>
+  <si>
     <t>家宴</t>
-  </si>
-  <si>
-    <t>剧本杀</t>
   </si>
   <si>
     <t>2026-02-27</t>
@@ -96,13 +180,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
@@ -581,144 +671,148 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1249,7 +1343,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
@@ -1268,7 +1362,7 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
@@ -1290,7 +1384,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4" t="s">
@@ -1301,124 +1395,344 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="2" t="s">
-        <v>9</v>
+      <c r="A6" t="s">
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="2" t="s">
-        <v>10</v>
+      <c r="A7" t="s">
+        <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>4</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="2" t="s">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="2" t="s">
-        <v>12</v>
+      <c r="A9" t="s">
+        <v>14</v>
       </c>
       <c r="B9" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" ht="15" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" ht="15" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
         <v>4</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="2" t="s">
-        <v>15</v>
+      <c r="A12" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="B12" t="s">
         <v>4</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="2" t="s">
-        <v>16</v>
+      <c r="A13" t="s">
+        <v>19</v>
       </c>
       <c r="B13" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
-        <v>17</v>
+      <c r="A14" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="B14" t="s">
         <v>4</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>5</v>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" ht="15" spans="1:3">
+      <c r="A17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" ht="15" spans="1:3">
+      <c r="A18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" t="s">
+        <v>4</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B35" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="24">
   <si>
     <t>update_name</t>
   </si>
@@ -84,6 +84,21 @@
   </si>
   <si>
     <t>我滴家在东北</t>
+  </si>
+  <si>
+    <t>花牌情缘</t>
+  </si>
+  <si>
+    <t>动漫</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>花田喜事</t>
+  </si>
+  <si>
+    <t>请将我深埋</t>
   </si>
 </sst>
 </file>
@@ -711,7 +726,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -724,6 +739,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1249,7 +1265,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
@@ -1411,7 +1427,7 @@
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B15" t="s">
@@ -1419,6 +1435,39 @@
       </c>
       <c r="C15" s="1" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
   <si>
     <t>update_name</t>
   </si>
@@ -38,67 +38,16 @@
     <t>update_date</t>
   </si>
   <si>
-    <t>家宴</t>
+    <t>江湖夜雨十年灯</t>
   </si>
   <si>
     <t>剧本杀</t>
   </si>
   <si>
-    <t>2026-02-27</t>
+    <t>2026-03-12</t>
   </si>
   <si>
-    <t>大宴之上</t>
-  </si>
-  <si>
-    <t>阴明寺</t>
-  </si>
-  <si>
-    <t>死者在幻夜中醒来</t>
-  </si>
-  <si>
-    <t>刑侦现场雪夜追凶</t>
-  </si>
-  <si>
-    <t>生还之日</t>
-  </si>
-  <si>
-    <t>一个死去的朋友</t>
-  </si>
-  <si>
-    <t>生门</t>
-  </si>
-  <si>
-    <t>东京恐怖故事：加藤病院</t>
-  </si>
-  <si>
-    <t>三界之下</t>
-  </si>
-  <si>
-    <t>猫岛2犬山谋杀循环</t>
-  </si>
-  <si>
-    <t>声声慢</t>
-  </si>
-  <si>
-    <t>声声慢2</t>
-  </si>
-  <si>
-    <t>我滴家在东北</t>
-  </si>
-  <si>
-    <t>花牌情缘</t>
-  </si>
-  <si>
-    <t>动漫</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
-    <t>花田喜事</t>
-  </si>
-  <si>
-    <t>请将我深埋</t>
+    <t>酒大奇迹</t>
   </si>
 </sst>
 </file>
@@ -122,13 +71,13 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="Segoe UI"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -726,13 +675,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1265,7 +1215,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
@@ -1295,7 +1245,7 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" t="s">
@@ -1305,170 +1255,47 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" t="s">
-        <v>4</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>21</v>
-      </c>
+    <row r="4" spans="1:1">
+      <c r="A4" s="3"/>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="4"/>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="4"/>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="4"/>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="4"/>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="4"/>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="4"/>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="4"/>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="4"/>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="4"/>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="4"/>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="3"/>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="5"/>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
   <si>
     <t>update_name</t>
   </si>
@@ -49,6 +49,12 @@
   <si>
     <t>酒大奇迹</t>
   </si>
+  <si>
+    <t>立方馆谋杀始末</t>
+  </si>
+  <si>
+    <t>2026-03-15</t>
+  </si>
 </sst>
 </file>
 
@@ -71,13 +77,13 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="Segoe UI"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -683,13 +689,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1255,8 +1261,16 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="3"/>
+    <row r="4" spans="1:3">
+      <c r="A4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="4"/>
@@ -1289,13 +1303,13 @@
       <c r="A14" s="4"/>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="3"/>
+      <c r="A15" s="5"/>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="5"/>
+      <c r="A16" s="2"/>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="5"/>
+      <c r="A17" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
   <si>
     <t>update_name</t>
   </si>
@@ -54,6 +54,15 @@
   </si>
   <si>
     <t>2026-03-15</t>
+  </si>
+  <si>
+    <t>安闲领主的愉快领地防卫</t>
+  </si>
+  <si>
+    <t>动漫</t>
+  </si>
+  <si>
+    <t>2026-03-17</t>
   </si>
 </sst>
 </file>
@@ -1262,7 +1271,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B4" t="s">
@@ -1272,8 +1281,16 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="4"/>
+    <row r="5" spans="1:3">
+      <c r="A5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="4"/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
   <si>
     <t>update_name</t>
   </si>
@@ -63,6 +63,12 @@
   </si>
   <si>
     <t>2026-03-17</t>
+  </si>
+  <si>
+    <t>草芥</t>
+  </si>
+  <si>
+    <t>2026-03-19</t>
   </si>
 </sst>
 </file>
@@ -1282,18 +1288,26 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="4"/>
+    <row r="6" spans="1:3">
+      <c r="A6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="4"/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
   <si>
     <t>update_name</t>
   </si>
@@ -69,6 +69,12 @@
   </si>
   <si>
     <t>2026-03-19</t>
+  </si>
+  <si>
+    <t>人魈传说</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
   </si>
 </sst>
 </file>
@@ -1299,7 +1305,7 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B6" t="s">
@@ -1309,8 +1315,16 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="4"/>
+    <row r="7" spans="1:3">
+      <c r="A7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="4"/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
   <si>
     <t>update_name</t>
   </si>
@@ -75,6 +75,12 @@
   </si>
   <si>
     <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>她未能歌颂的明日</t>
+  </si>
+  <si>
+    <t>2026-03-26</t>
   </si>
 </sst>
 </file>
@@ -1316,7 +1322,7 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B7" t="s">
@@ -1326,8 +1332,16 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="4"/>
+    <row r="8" spans="1:3">
+      <c r="A8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="4"/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
   <si>
     <t>update_name</t>
   </si>
@@ -81,6 +81,12 @@
   </si>
   <si>
     <t>2026-03-26</t>
+  </si>
+  <si>
+    <t>天启诡案</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
   </si>
 </sst>
 </file>
@@ -1333,7 +1339,7 @@
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B8" t="s">
@@ -1343,8 +1349,16 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="4"/>
+    <row r="9" spans="1:3">
+      <c r="A9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="4"/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
   <si>
     <t>update_name</t>
   </si>
@@ -87,6 +87,15 @@
   </si>
   <si>
     <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>祝福</t>
+  </si>
+  <si>
+    <t>2026-03-28</t>
+  </si>
+  <si>
+    <t>尸乐园</t>
   </si>
 </sst>
 </file>
@@ -1350,7 +1359,7 @@
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B9" t="s">
@@ -1360,11 +1369,27 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="4"/>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="4"/>
+    <row r="10" spans="1:3">
+      <c r="A10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="4"/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
   <si>
     <t>update_name</t>
   </si>
@@ -38,36 +38,12 @@
     <t>update_date</t>
   </si>
   <si>
-    <t>江湖夜雨十年灯</t>
+    <t>草芥</t>
   </si>
   <si>
     <t>剧本杀</t>
   </si>
   <si>
-    <t>2026-03-12</t>
-  </si>
-  <si>
-    <t>酒大奇迹</t>
-  </si>
-  <si>
-    <t>立方馆谋杀始末</t>
-  </si>
-  <si>
-    <t>2026-03-15</t>
-  </si>
-  <si>
-    <t>安闲领主的愉快领地防卫</t>
-  </si>
-  <si>
-    <t>动漫</t>
-  </si>
-  <si>
-    <t>2026-03-17</t>
-  </si>
-  <si>
-    <t>草芥</t>
-  </si>
-  <si>
     <t>2026-03-19</t>
   </si>
   <si>
@@ -96,6 +72,12 @@
   </si>
   <si>
     <t>尸乐园</t>
+  </si>
+  <si>
+    <t>洗劫伦敦所有的玫瑰</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
   </si>
 </sst>
 </file>
@@ -1263,7 +1245,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
@@ -1300,26 +1282,26 @@
         <v>4</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="2" t="s">
         <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>11</v>
@@ -1344,70 +1326,34 @@
         <v>4</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="2" t="s">
-        <v>16</v>
+      <c r="A8" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="B8" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>19</v>
-      </c>
+    <row r="9" spans="1:1">
+      <c r="A9" s="4"/>
     </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>21</v>
-      </c>
+    <row r="10" spans="1:1">
+      <c r="A10" s="4"/>
     </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>21</v>
-      </c>
+    <row r="11" spans="1:1">
+      <c r="A11" s="5"/>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="4"/>
+      <c r="A12" s="2"/>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="4"/>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="4"/>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="5"/>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="2"/>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="2"/>
+      <c r="A13" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>update_name</t>
   </si>
@@ -38,46 +38,25 @@
     <t>update_date</t>
   </si>
   <si>
-    <t>草芥</t>
+    <t>尸乐园</t>
   </si>
   <si>
     <t>剧本杀</t>
   </si>
   <si>
-    <t>2026-03-19</t>
-  </si>
-  <si>
-    <t>人魈传说</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>她未能歌颂的明日</t>
-  </si>
-  <si>
-    <t>2026-03-26</t>
-  </si>
-  <si>
-    <t>天启诡案</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>祝福</t>
-  </si>
-  <si>
     <t>2026-03-28</t>
-  </si>
-  <si>
-    <t>尸乐园</t>
   </si>
   <si>
     <t>洗劫伦敦所有的玫瑰</t>
   </si>
   <si>
     <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>六角馆的谋杀鉴赏</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
   </si>
 </sst>
 </file>
@@ -101,13 +80,13 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="Segoe UI"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -705,14 +684,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -1245,8 +1223,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
     <col min="3" max="3" width="11.6363636363636" style="1" customWidth="1"/>
@@ -1286,7 +1264,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="s">
@@ -1296,64 +1274,17 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>11</v>
-      </c>
+    <row r="5" spans="1:1">
+      <c r="A5" s="4"/>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>13</v>
-      </c>
+    <row r="6" spans="1:1">
+      <c r="A6" s="3"/>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>13</v>
-      </c>
+    <row r="7" spans="1:1">
+      <c r="A7" s="2"/>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="4"/>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="4"/>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="5"/>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="2"/>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="2"/>
+    <row r="8" spans="1:1">
+      <c r="A8" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
   <si>
     <t>update_name</t>
   </si>
@@ -58,6 +58,15 @@
   <si>
     <t>2026-04-09</t>
   </si>
+  <si>
+    <t>王不见王</t>
+  </si>
+  <si>
+    <t>2026-04-11</t>
+  </si>
+  <si>
+    <t>因火成烟</t>
+  </si>
 </sst>
 </file>
 
@@ -69,7 +78,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -81,12 +90,6 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -554,133 +557,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -695,9 +698,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1274,11 +1275,27 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="4"/>
+    <row r="5" spans="1:3">
+      <c r="A5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="3"/>
+    <row r="6" spans="1:3">
+      <c r="A6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="2"/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
   <si>
     <t>update_name</t>
   </si>
@@ -66,6 +66,12 @@
   </si>
   <si>
     <t>因火成烟</t>
+  </si>
+  <si>
+    <t>木夕僧之戏</t>
+  </si>
+  <si>
+    <t>2026-04-15</t>
   </si>
 </sst>
 </file>
@@ -1276,7 +1282,7 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B5" t="s">
@@ -1297,8 +1303,16 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="2"/>
+    <row r="7" spans="1:3">
+      <c r="A7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="2"/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
   <si>
     <t>update_name</t>
   </si>
@@ -72,6 +72,12 @@
   </si>
   <si>
     <t>2026-04-15</t>
+  </si>
+  <si>
+    <t>暗波崖</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
   </si>
 </sst>
 </file>
@@ -1304,7 +1310,7 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B7" t="s">
@@ -1314,8 +1320,16 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="2"/>
+    <row r="8" spans="1:3">
+      <c r="A8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
   <si>
     <t>update_name</t>
   </si>
@@ -38,22 +38,10 @@
     <t>update_date</t>
   </si>
   <si>
-    <t>尸乐园</t>
+    <t>六角馆的谋杀鉴赏</t>
   </si>
   <si>
     <t>剧本杀</t>
-  </si>
-  <si>
-    <t>2026-03-28</t>
-  </si>
-  <si>
-    <t>洗劫伦敦所有的玫瑰</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>六角馆的谋杀鉴赏</t>
   </si>
   <si>
     <t>2026-04-09</t>
@@ -706,10 +694,10 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1236,8 +1224,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="2"/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
     <col min="3" max="3" width="11.6363636363636" style="1" customWidth="1"/>
@@ -1266,7 +1254,7 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B3" t="s">
@@ -1277,58 +1265,36 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="2" t="s">
-        <v>10</v>
+      <c r="A5" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
-        <v>12</v>
+      <c r="A6" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/update.xlsx
+++ b/update.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
   <si>
     <t>update_name</t>
   </si>
@@ -66,6 +66,12 @@
   </si>
   <si>
     <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>难生恨</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
   </si>
 </sst>
 </file>
@@ -1224,8 +1230,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="2"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
     <col min="3" max="3" width="11.6363636363636" style="1" customWidth="1"/>
@@ -1287,7 +1293,7 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B6" t="s">
@@ -1295,6 +1301,17 @@
       </c>
       <c r="C6" s="1" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
   <si>
     <t>update_name</t>
   </si>
@@ -72,6 +72,15 @@
   </si>
   <si>
     <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>大楼里只有谋杀only murder</t>
+  </si>
+  <si>
+    <t>剧集</t>
+  </si>
+  <si>
+    <t>2026-04-25</t>
   </si>
 </sst>
 </file>
@@ -693,7 +702,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -703,7 +712,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1230,8 +1238,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="2"/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
     <col min="3" max="3" width="11.6363636363636" style="1" customWidth="1"/>
@@ -1304,7 +1312,7 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B7" t="s">
@@ -1312,6 +1320,17 @@
       </c>
       <c r="C7" s="1" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
   <si>
     <t>update_name</t>
   </si>
@@ -81,6 +81,12 @@
   </si>
   <si>
     <t>2026-04-25</t>
+  </si>
+  <si>
+    <t>沃德朴一家</t>
+  </si>
+  <si>
+    <t>动漫</t>
   </si>
 </sst>
 </file>
@@ -1238,8 +1244,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="2"/>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
     <col min="3" max="3" width="11.6363636363636" style="1" customWidth="1"/>
@@ -1333,6 +1339,17 @@
         <v>17</v>
       </c>
     </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
   <si>
     <t>update_name</t>
   </si>
@@ -87,6 +87,12 @@
   </si>
   <si>
     <t>动漫</t>
+  </si>
+  <si>
+    <t>阿依达</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
   </si>
 </sst>
 </file>
@@ -1244,7 +1250,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
@@ -1350,6 +1356,17 @@
         <v>17</v>
       </c>
     </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="10">
   <si>
     <t>update_name</t>
   </si>
@@ -38,61 +38,25 @@
     <t>update_date</t>
   </si>
   <si>
-    <t>六角馆的谋杀鉴赏</t>
+    <t>阿依达</t>
   </si>
   <si>
     <t>剧本杀</t>
   </si>
   <si>
-    <t>2026-04-09</t>
+    <t>2026-04-29</t>
   </si>
   <si>
-    <t>王不见王</t>
+    <t>决战洗剪吹</t>
   </si>
   <si>
-    <t>2026-04-11</t>
+    <t>2026-04-30</t>
   </si>
   <si>
-    <t>因火成烟</t>
+    <t>动物监友会</t>
   </si>
   <si>
-    <t>木夕僧之戏</t>
-  </si>
-  <si>
-    <t>2026-04-15</t>
-  </si>
-  <si>
-    <t>暗波崖</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
-  </si>
-  <si>
-    <t>难生恨</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>大楼里只有谋杀only murder</t>
-  </si>
-  <si>
-    <t>剧集</t>
-  </si>
-  <si>
-    <t>2026-04-25</t>
-  </si>
-  <si>
-    <t>沃德朴一家</t>
-  </si>
-  <si>
-    <t>动漫</t>
-  </si>
-  <si>
-    <t>阿依达</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
+    <t>人脑不宜食用</t>
   </si>
 </sst>
 </file>
@@ -105,19 +69,13 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -584,133 +542,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -721,9 +679,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1250,8 +1206,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
     <col min="3" max="3" width="11.6363636363636" style="1" customWidth="1"/>
@@ -1291,7 +1247,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="s">
@@ -1302,69 +1258,14 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" t="s">
         <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="12">
   <si>
     <t>update_name</t>
   </si>
@@ -57,6 +57,12 @@
   </si>
   <si>
     <t>人脑不宜食用</t>
+  </si>
+  <si>
+    <t>不喜</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
   </si>
 </sst>
 </file>
@@ -680,7 +686,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1206,8 +1214,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="2"/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
     <col min="3" max="3" width="11.6363636363636" style="1" customWidth="1"/>
@@ -1236,7 +1244,7 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" t="s">
@@ -1247,7 +1255,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="s">
@@ -1266,6 +1274,17 @@
       </c>
       <c r="C5" s="1" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
   <si>
     <t>update_name</t>
   </si>
@@ -63,6 +63,15 @@
   </si>
   <si>
     <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>持斧奥夫</t>
+  </si>
+  <si>
+    <t>2026-05-12</t>
+  </si>
+  <si>
+    <t>风林火山</t>
   </si>
 </sst>
 </file>
@@ -678,7 +687,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -689,6 +698,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1214,8 +1224,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="2"/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
     <col min="3" max="3" width="11.6363636363636" style="1" customWidth="1"/>
@@ -1287,6 +1297,28 @@
         <v>11</v>
       </c>
     </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="17">
   <si>
     <t>update_name</t>
   </si>
@@ -72,6 +72,12 @@
   </si>
   <si>
     <t>风林火山</t>
+  </si>
+  <si>
+    <t>漓川怪谈簿</t>
+  </si>
+  <si>
+    <t>2026-05-17</t>
   </si>
 </sst>
 </file>
@@ -687,7 +693,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -698,7 +704,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1224,8 +1229,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="2"/>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
     <col min="3" max="3" width="11.6363636363636" style="1" customWidth="1"/>
@@ -1298,7 +1303,7 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B7" t="s">
@@ -1309,7 +1314,7 @@
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B8" t="s">
@@ -1317,6 +1322,17 @@
       </c>
       <c r="C8" s="1" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
   <si>
     <t>update_name</t>
   </si>
@@ -38,28 +38,10 @@
     <t>update_date</t>
   </si>
   <si>
-    <t>阿依达</t>
+    <t>不喜</t>
   </si>
   <si>
     <t>剧本杀</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>决战洗剪吹</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>动物监友会</t>
-  </si>
-  <si>
-    <t>人脑不宜食用</t>
-  </si>
-  <si>
-    <t>不喜</t>
   </si>
   <si>
     <t>2026-05-06</t>
@@ -78,6 +60,12 @@
   </si>
   <si>
     <t>2026-05-17</t>
+  </si>
+  <si>
+    <t>洗劫伦敦所有的玫瑰</t>
+  </si>
+  <si>
+    <t>2026-05-29</t>
   </si>
 </sst>
 </file>
@@ -700,10 +688,10 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1229,8 +1217,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
     <col min="3" max="3" width="11.6363636363636" style="1" customWidth="1"/>
@@ -1259,7 +1247,7 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B3" t="s">
@@ -1270,7 +1258,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="s">
@@ -1288,51 +1276,18 @@
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
-        <v>10</v>
+      <c r="A6" t="s">
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
   <si>
     <t>update_name</t>
   </si>
@@ -38,34 +38,19 @@
     <t>update_date</t>
   </si>
   <si>
-    <t>不喜</t>
+    <t>洗劫伦敦所有的玫瑰</t>
   </si>
   <si>
     <t>剧本杀</t>
   </si>
   <si>
-    <t>2026-05-06</t>
+    <t>2026-05-29</t>
   </si>
   <si>
-    <t>持斧奥夫</t>
+    <t>甜蜜的家</t>
   </si>
   <si>
-    <t>2026-05-12</t>
-  </si>
-  <si>
-    <t>风林火山</t>
-  </si>
-  <si>
-    <t>漓川怪谈簿</t>
-  </si>
-  <si>
-    <t>2026-05-17</t>
-  </si>
-  <si>
-    <t>洗劫伦敦所有的玫瑰</t>
-  </si>
-  <si>
-    <t>2026-05-29</t>
+    <t>2026-06-02</t>
   </si>
 </sst>
 </file>
@@ -681,14 +666,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
@@ -1217,8 +1199,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="2"/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
     <col min="3" max="3" width="11.6363636363636" style="1" customWidth="1"/>
@@ -1236,7 +1218,7 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
@@ -1247,7 +1229,7 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" t="s">
@@ -1257,39 +1239,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>update_name</t>
   </si>
@@ -51,6 +51,12 @@
   </si>
   <si>
     <t>2026-06-02</t>
+  </si>
+  <si>
+    <t>偷吃</t>
+  </si>
+  <si>
+    <t>2026-06-03</t>
   </si>
 </sst>
 </file>
@@ -1199,8 +1205,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="2"/>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
     <col min="3" max="3" width="11.6363636363636" style="1" customWidth="1"/>
@@ -1239,6 +1245,17 @@
         <v>7</v>
       </c>
     </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
   <si>
     <t>update_name</t>
   </si>
@@ -57,6 +57,15 @@
   </si>
   <si>
     <t>2026-06-03</t>
+  </si>
+  <si>
+    <t>如故</t>
+  </si>
+  <si>
+    <t>2026-06-09</t>
+  </si>
+  <si>
+    <t>野菩萨</t>
   </si>
 </sst>
 </file>
@@ -672,13 +681,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1205,8 +1215,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="2"/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
     <col min="3" max="3" width="11.6363636363636" style="1" customWidth="1"/>
@@ -1256,6 +1266,28 @@
         <v>9</v>
       </c>
     </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
   <si>
     <t>update_name</t>
   </si>
@@ -66,6 +66,15 @@
   </si>
   <si>
     <t>野菩萨</t>
+  </si>
+  <si>
+    <t>继承者</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>鬼河怒放</t>
   </si>
 </sst>
 </file>
@@ -78,13 +87,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="Roboto"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -551,133 +566,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -689,7 +704,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1215,8 +1230,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="2"/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
     <col min="3" max="3" width="11.6363636363636" style="1" customWidth="1"/>
@@ -1267,7 +1282,7 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B5" t="s">
@@ -1278,7 +1293,7 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B6" t="s">
@@ -1286,6 +1301,28 @@
       </c>
       <c r="C6" s="1" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="18">
   <si>
     <t>update_name</t>
   </si>
@@ -75,6 +75,12 @@
   </si>
   <si>
     <t>鬼河怒放</t>
+  </si>
+  <si>
+    <t>雪夜城谜案</t>
+  </si>
+  <si>
+    <t>2026-06-14</t>
   </si>
 </sst>
 </file>
@@ -1230,8 +1236,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="2"/>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
     <col min="3" max="3" width="11.6363636363636" style="1" customWidth="1"/>
@@ -1325,6 +1331,17 @@
         <v>14</v>
       </c>
     </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
   <si>
     <t>update_name</t>
   </si>
@@ -81,6 +81,15 @@
   </si>
   <si>
     <t>2026-06-14</t>
+  </si>
+  <si>
+    <t>老鼠记者</t>
+  </si>
+  <si>
+    <t>动漫</t>
+  </si>
+  <si>
+    <t>2026-06-15</t>
   </si>
 </sst>
 </file>
@@ -1236,7 +1245,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
@@ -1342,6 +1351,17 @@
         <v>17</v>
       </c>
     </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -38,18 +38,12 @@
     <t>update_date</t>
   </si>
   <si>
-    <t>洗劫伦敦所有的玫瑰</t>
+    <t>甜蜜的家</t>
   </si>
   <si>
     <t>剧本杀</t>
   </si>
   <si>
-    <t>2026-05-29</t>
-  </si>
-  <si>
-    <t>甜蜜的家</t>
-  </si>
-  <si>
     <t>2026-06-02</t>
   </si>
   <si>
@@ -90,6 +84,12 @@
   </si>
   <si>
     <t>2026-06-15</t>
+  </si>
+  <si>
+    <t>归昼</t>
+  </si>
+  <si>
+    <t>2026-06-16</t>
   </si>
 </sst>
 </file>
@@ -1264,7 +1264,7 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
@@ -1275,7 +1275,7 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" t="s">
         <v>6</v>
       </c>
       <c r="B3" t="s">
@@ -1286,7 +1286,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="s">
@@ -1304,18 +1304,18 @@
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="2" t="s">
-        <v>12</v>
+      <c r="A6" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1326,18 +1326,18 @@
         <v>4</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="3" t="s">
-        <v>15</v>
+      <c r="A8" t="s">
+        <v>14</v>
       </c>
       <c r="B8" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1345,18 +1345,18 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>20</v>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="18">
   <si>
     <t>update_name</t>
   </si>
@@ -38,33 +38,12 @@
     <t>update_date</t>
   </si>
   <si>
-    <t>甜蜜的家</t>
+    <t>继承者</t>
   </si>
   <si>
     <t>剧本杀</t>
   </si>
   <si>
-    <t>2026-06-02</t>
-  </si>
-  <si>
-    <t>偷吃</t>
-  </si>
-  <si>
-    <t>2026-06-03</t>
-  </si>
-  <si>
-    <t>如故</t>
-  </si>
-  <si>
-    <t>2026-06-09</t>
-  </si>
-  <si>
-    <t>野菩萨</t>
-  </si>
-  <si>
-    <t>继承者</t>
-  </si>
-  <si>
     <t>2026-06-11</t>
   </si>
   <si>
@@ -90,6 +69,18 @@
   </si>
   <si>
     <t>2026-06-16</t>
+  </si>
+  <si>
+    <t>血色唐人街</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>再见苏西</t>
+  </si>
+  <si>
+    <t>女帝攻略</t>
   </si>
 </sst>
 </file>
@@ -718,8 +709,8 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1245,7 +1236,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
@@ -1275,63 +1266,63 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="2" t="s">
-        <v>8</v>
+      <c r="A4" t="s">
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
       <c r="C5" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
-        <v>11</v>
+      <c r="A6" t="s">
+        <v>12</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
         <v>4</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>14</v>
+      <c r="A8" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="B8" t="s">
         <v>4</v>
@@ -1341,25 +1332,14 @@
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>16</v>
+      <c r="A9" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
   <si>
     <t>update_name</t>
   </si>
@@ -38,34 +38,10 @@
     <t>update_date</t>
   </si>
   <si>
-    <t>继承者</t>
+    <t>归昼</t>
   </si>
   <si>
     <t>剧本杀</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
-  </si>
-  <si>
-    <t>鬼河怒放</t>
-  </si>
-  <si>
-    <t>雪夜城谜案</t>
-  </si>
-  <si>
-    <t>2026-06-14</t>
-  </si>
-  <si>
-    <t>老鼠记者</t>
-  </si>
-  <si>
-    <t>动漫</t>
-  </si>
-  <si>
-    <t>2026-06-15</t>
-  </si>
-  <si>
-    <t>归昼</t>
   </si>
   <si>
     <t>2026-06-16</t>
@@ -82,6 +58,15 @@
   <si>
     <t>女帝攻略</t>
   </si>
+  <si>
+    <t>金粉</t>
+  </si>
+  <si>
+    <t>2026-06-20</t>
+  </si>
+  <si>
+    <t>绿洲</t>
+  </si>
 </sst>
 </file>
 
@@ -93,19 +78,13 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color theme="1"/>
-      <name val="Roboto"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -572,133 +551,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -709,7 +688,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1236,8 +1215,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
     <col min="3" max="3" width="11.6363636363636" style="1" customWidth="1"/>
@@ -1255,7 +1234,7 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
@@ -1273,73 +1252,51 @@
         <v>4</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>7</v>
+      <c r="A4" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>12</v>
+      <c r="A6" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>4</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/update.xlsx
+++ b/update.xlsx
@@ -1,26 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Download\quark-dynamic\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF4DD074-18B5-477A-AEB0-33D472FE7206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="18">
   <si>
     <t>update_name</t>
   </si>
@@ -64,18 +71,29 @@
     <t>游轮谜影</t>
   </si>
   <si>
+    <t>2026-06-24</t>
+  </si>
+  <si>
     <t>疯人塔</t>
   </si>
   <si>
-    <t>2026-06-24</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>北京爱情图鉴</t>
+  </si>
+  <si>
+    <t>2026-06-27</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -87,27 +105,349 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -115,13 +455,255 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -132,159 +714,91 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
+        <b val="1"/>
         <color theme="1"/>
       </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
       <border>
@@ -295,7 +809,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -323,40 +837,154 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
+          <color theme="4" tint="0.399975585192419"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstColumn" dxfId="13"/>
-      <tableStyleElement type="lastColumn" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
-      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -606,20 +1234,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="2" width="22.6328125" customWidth="1"/>
-    <col min="3" max="3" width="11.6328125" style="1" customWidth="1"/>
+    <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
+    <col min="3" max="3" width="11.6363636363636" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -630,7 +1258,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -641,7 +1269,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -652,7 +1280,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -663,7 +1291,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -674,7 +1302,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -685,7 +1313,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
@@ -696,7 +1324,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
@@ -704,22 +1332,33 @@
         <v>4</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="2" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="B9" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
   <si>
     <t>update_name</t>
   </si>
@@ -38,37 +38,10 @@
     <t>update_date</t>
   </si>
   <si>
-    <t>归昼</t>
+    <t>游轮谜影</t>
   </si>
   <si>
     <t>剧本杀</t>
-  </si>
-  <si>
-    <t>2026-06-16</t>
-  </si>
-  <si>
-    <t>血色唐人街</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>再见苏西</t>
-  </si>
-  <si>
-    <t>女帝攻略</t>
-  </si>
-  <si>
-    <t>金粉</t>
-  </si>
-  <si>
-    <t>2026-06-20</t>
-  </si>
-  <si>
-    <t>绿洲</t>
-  </si>
-  <si>
-    <t>游轮谜影</t>
   </si>
   <si>
     <t>2026-06-24</t>
@@ -82,6 +55,21 @@
   <si>
     <t>2026-06-27</t>
   </si>
+  <si>
+    <t>星火号</t>
+  </si>
+  <si>
+    <t>2026-07-05</t>
+  </si>
+  <si>
+    <t>魔女的考验</t>
+  </si>
+  <si>
+    <t>动漫</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
 </sst>
 </file>
 
@@ -93,14 +81,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -573,137 +554,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -711,9 +692,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1240,8 +1222,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
     <col min="3" max="3" width="11.6363636363636" style="1" customWidth="1"/>
@@ -1259,13 +1241,13 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1276,85 +1258,41 @@
       <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>7</v>
+      <c r="C3" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="2" t="s">
-        <v>8</v>
+      <c r="A4" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>7</v>
+      <c r="C4" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>7</v>
+      <c r="C5" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="2" t="s">
-        <v>10</v>
+      <c r="A6" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
   <si>
     <t>update_name</t>
   </si>
@@ -69,6 +69,12 @@
   </si>
   <si>
     <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>窃云台</t>
+  </si>
+  <si>
+    <t>2026-07-11</t>
   </si>
 </sst>
 </file>
@@ -1222,8 +1228,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="2"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
     <col min="3" max="3" width="11.6363636363636" style="1" customWidth="1"/>
@@ -1285,7 +1291,7 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B6" t="s">
@@ -1293,6 +1299,17 @@
       </c>
       <c r="C6" s="3" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
   <si>
     <t>update_name</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t>2026-07-11</t>
+  </si>
+  <si>
+    <t>塑料温室</t>
   </si>
 </sst>
 </file>
@@ -1228,8 +1231,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="2"/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
     <col min="3" max="3" width="11.6363636363636" style="1" customWidth="1"/>
@@ -1312,6 +1315,17 @@
         <v>15</v>
       </c>
     </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
   <si>
     <t>update_name</t>
   </si>
@@ -78,6 +78,12 @@
   </si>
   <si>
     <t>塑料温室</t>
+  </si>
+  <si>
+    <t>二流货色2</t>
+  </si>
+  <si>
+    <t>2026-07-14</t>
   </si>
 </sst>
 </file>
@@ -693,7 +699,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -704,7 +710,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1231,8 +1236,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="2"/>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
     <col min="3" max="3" width="11.6363636363636" style="1" customWidth="1"/>
@@ -1305,7 +1310,7 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B7" t="s">
@@ -1316,7 +1321,7 @@
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B8" t="s">
@@ -1324,6 +1329,17 @@
       </c>
       <c r="C8" s="3" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
   <si>
     <t>update_name</t>
   </si>
@@ -84,6 +84,12 @@
   </si>
   <si>
     <t>2026-07-14</t>
+  </si>
+  <si>
+    <t>白昼2如果长夜无明</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
   </si>
 </sst>
 </file>
@@ -96,13 +102,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -569,137 +581,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -711,6 +723,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1236,7 +1249,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
@@ -1342,6 +1355,17 @@
         <v>18</v>
       </c>
     </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
   <si>
     <t>update_name</t>
   </si>
@@ -38,40 +38,10 @@
     <t>update_date</t>
   </si>
   <si>
-    <t>游轮谜影</t>
+    <t>窃云台</t>
   </si>
   <si>
     <t>剧本杀</t>
-  </si>
-  <si>
-    <t>2026-06-24</t>
-  </si>
-  <si>
-    <t>疯人塔</t>
-  </si>
-  <si>
-    <t>北京爱情图鉴</t>
-  </si>
-  <si>
-    <t>2026-06-27</t>
-  </si>
-  <si>
-    <t>星火号</t>
-  </si>
-  <si>
-    <t>2026-07-05</t>
-  </si>
-  <si>
-    <t>魔女的考验</t>
-  </si>
-  <si>
-    <t>动漫</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>窃云台</t>
   </si>
   <si>
     <t>2026-07-11</t>
@@ -90,6 +60,12 @@
   </si>
   <si>
     <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>流芳</t>
+  </si>
+  <si>
+    <t>2026-07-26</t>
   </si>
 </sst>
 </file>
@@ -718,12 +694,12 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1249,8 +1225,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
     <col min="3" max="3" width="11.6363636363636" style="1" customWidth="1"/>
@@ -1290,7 +1266,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="4" t="s">
+      <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4" t="s">
@@ -1312,58 +1288,14 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
   <si>
     <t>update_name</t>
   </si>
@@ -66,6 +66,12 @@
   </si>
   <si>
     <t>2026-07-26</t>
+  </si>
+  <si>
+    <t>壁上观</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
   </si>
 </sst>
 </file>
@@ -78,7 +84,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -90,6 +96,12 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -557,133 +569,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -699,7 +711,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1225,8 +1237,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="2"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
     <col min="3" max="3" width="11.6363636363636" style="1" customWidth="1"/>
@@ -1288,7 +1300,7 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B6" t="s">
@@ -1296,6 +1308,17 @@
       </c>
       <c r="C6" s="3" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
   <si>
     <t>update_name</t>
   </si>
@@ -72,6 +72,9 @@
   </si>
   <si>
     <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>同流合屋</t>
   </si>
 </sst>
 </file>
@@ -1237,8 +1240,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="2"/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
     <col min="3" max="3" width="11.6363636363636" style="1" customWidth="1"/>
@@ -1321,6 +1324,17 @@
         <v>14</v>
       </c>
     </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
   <si>
     <t>update_name</t>
   </si>
@@ -75,6 +75,15 @@
   </si>
   <si>
     <t>同流合屋</t>
+  </si>
+  <si>
+    <t>头颅们的失眠夜</t>
+  </si>
+  <si>
+    <t>2026-08-01</t>
+  </si>
+  <si>
+    <t>葡萄不是幸福的水果</t>
   </si>
 </sst>
 </file>
@@ -702,7 +711,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -715,6 +724,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1240,8 +1250,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="2"/>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
     <col min="3" max="3" width="11.6363636363636" style="1" customWidth="1"/>
@@ -1335,6 +1345,28 @@
         <v>14</v>
       </c>
     </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="14">
   <si>
     <t>update_name</t>
   </si>
@@ -38,31 +38,10 @@
     <t>update_date</t>
   </si>
   <si>
-    <t>窃云台</t>
+    <t>流芳</t>
   </si>
   <si>
     <t>剧本杀</t>
-  </si>
-  <si>
-    <t>2026-07-11</t>
-  </si>
-  <si>
-    <t>塑料温室</t>
-  </si>
-  <si>
-    <t>二流货色2</t>
-  </si>
-  <si>
-    <t>2026-07-14</t>
-  </si>
-  <si>
-    <t>白昼2如果长夜无明</t>
-  </si>
-  <si>
-    <t>2026-07-15</t>
-  </si>
-  <si>
-    <t>流芳</t>
   </si>
   <si>
     <t>2026-07-26</t>
@@ -85,6 +64,12 @@
   <si>
     <t>葡萄不是幸福的水果</t>
   </si>
+  <si>
+    <t>疯兔子，白又白，砍下脑袋飞起来</t>
+  </si>
+  <si>
+    <t>2026-08-04</t>
+  </si>
 </sst>
 </file>
 
@@ -96,19 +81,13 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Segoe UI"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
@@ -581,137 +560,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -723,8 +702,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1250,8 +1227,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
     <col min="3" max="3" width="11.6363636363636" style="1" customWidth="1"/>
@@ -1280,29 +1257,29 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B5" t="s">
@@ -1320,51 +1297,18 @@
         <v>4</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="5" t="s">
-        <v>13</v>
+      <c r="A7" t="s">
+        <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>4</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
   <si>
     <t>update_name</t>
   </si>
@@ -69,6 +69,12 @@
   </si>
   <si>
     <t>2026-08-04</t>
+  </si>
+  <si>
+    <t>野狗不需要墓碑2：天生坏种</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
   </si>
 </sst>
 </file>
@@ -81,7 +87,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,6 +99,12 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -560,137 +572,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -702,6 +714,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1227,8 +1240,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="2"/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
     <col min="3" max="3" width="11.6363636363636" style="1" customWidth="1"/>
@@ -1311,6 +1324,17 @@
         <v>13</v>
       </c>
     </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="14">
   <si>
     <t>update_name</t>
   </si>
@@ -38,43 +38,37 @@
     <t>update_date</t>
   </si>
   <si>
-    <t>流芳</t>
+    <t>蜘蛛侠：平行宇宙</t>
   </si>
   <si>
-    <t>剧本杀</t>
+    <t>动漫</t>
   </si>
   <si>
-    <t>2026-07-26</t>
+    <t>2026-08-23</t>
   </si>
   <si>
-    <t>壁上观</t>
+    <t>蜘蛛侠：纵横宇宙</t>
   </si>
   <si>
-    <t>2026-07-29</t>
+    <t>超凡蜘蛛侠</t>
   </si>
   <si>
-    <t>同流合屋</t>
+    <t>蜘蛛侠 托比·马奎尔版</t>
   </si>
   <si>
-    <t>头颅们的失眠夜</t>
+    <t>蜘蛛侠：英雄归来</t>
   </si>
   <si>
-    <t>2026-08-01</t>
+    <t>蜘蛛侠：英雄远征</t>
   </si>
   <si>
-    <t>葡萄不是幸福的水果</t>
+    <t>蜘蛛侠：英雄无归</t>
   </si>
   <si>
-    <t>疯兔子，白又白，砍下脑袋飞起来</t>
+    <t>蜘蛛侠：崭新之日</t>
   </si>
   <si>
-    <t>2026-08-04</t>
-  </si>
-  <si>
-    <t>野狗不需要墓碑2：天生坏种</t>
-  </si>
-  <si>
-    <t>2026-08-14</t>
+    <t>终极蜘蛛侠</t>
   </si>
 </sst>
 </file>
@@ -96,15 +90,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="宋体"/>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Segoe UI"/>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1240,8 +1234,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="2"/>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
     <col min="3" max="3" width="11.6363636363636" style="1" customWidth="1"/>
@@ -1270,69 +1264,91 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>8</v>
+      <c r="A4" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="2" t="s">
-        <v>11</v>
+    <row r="6" ht="15.5" spans="1:3">
+      <c r="A6" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" ht="15.5" spans="1:3">
+      <c r="A7" s="4" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>4</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" ht="15" spans="1:3">
       <c r="A8" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>15</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="17">
   <si>
     <t>update_name</t>
   </si>
@@ -69,6 +69,15 @@
   </si>
   <si>
     <t>终极蜘蛛侠</t>
+  </si>
+  <si>
+    <t>东京恐怖故事：如月车站</t>
+  </si>
+  <si>
+    <t>剧本杀</t>
+  </si>
+  <si>
+    <t>2026-08-24</t>
   </si>
 </sst>
 </file>
@@ -81,7 +90,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -100,6 +109,13 @@
       <color rgb="FF333333"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -566,137 +582,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -709,6 +725,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1234,7 +1253,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
@@ -1351,6 +1370,17 @@
         <v>5</v>
       </c>
     </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
   <si>
     <t>update_name</t>
   </si>
@@ -38,39 +38,6 @@
     <t>update_date</t>
   </si>
   <si>
-    <t>蜘蛛侠：平行宇宙</t>
-  </si>
-  <si>
-    <t>动漫</t>
-  </si>
-  <si>
-    <t>2026-08-23</t>
-  </si>
-  <si>
-    <t>蜘蛛侠：纵横宇宙</t>
-  </si>
-  <si>
-    <t>超凡蜘蛛侠</t>
-  </si>
-  <si>
-    <t>蜘蛛侠 托比·马奎尔版</t>
-  </si>
-  <si>
-    <t>蜘蛛侠：英雄归来</t>
-  </si>
-  <si>
-    <t>蜘蛛侠：英雄远征</t>
-  </si>
-  <si>
-    <t>蜘蛛侠：英雄无归</t>
-  </si>
-  <si>
-    <t>蜘蛛侠：崭新之日</t>
-  </si>
-  <si>
-    <t>终极蜘蛛侠</t>
-  </si>
-  <si>
     <t>东京恐怖故事：如月车站</t>
   </si>
   <si>
@@ -78,6 +45,12 @@
   </si>
   <si>
     <t>2026-08-24</t>
+  </si>
+  <si>
+    <t>体温</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
   </si>
 </sst>
 </file>
@@ -90,25 +63,13 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF333333"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF333333"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -582,151 +543,148 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1253,8 +1211,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
     <col min="3" max="3" width="11.6363636363636" style="1" customWidth="1"/>
@@ -1283,102 +1241,14 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" t="s">
         <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" ht="15.5" spans="1:3">
-      <c r="A6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" ht="15.5" spans="1:3">
-      <c r="A7" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" ht="15" spans="1:3">
-      <c r="A8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
   <si>
     <t>update_name</t>
   </si>
@@ -51,6 +51,21 @@
   </si>
   <si>
     <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>【2026考研英语】石雷鹏橙啦全程班</t>
+  </si>
+  <si>
+    <t>学习资料</t>
+  </si>
+  <si>
+    <t>橙啦六级全程班[石雷鹏]</t>
+  </si>
+  <si>
+    <t>408计算机统考历年真题</t>
+  </si>
+  <si>
+    <t>1980-2025考研英语学习资料合集</t>
   </si>
 </sst>
 </file>
@@ -673,7 +688,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -686,6 +701,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1211,8 +1227,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="2"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
     <col min="3" max="3" width="11.6363636363636" style="1" customWidth="1"/>
@@ -1251,6 +1267,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
   <si>
     <t>update_name</t>
   </si>
@@ -66,6 +66,12 @@
   </si>
   <si>
     <t>1980-2025考研英语学习资料合集</t>
+  </si>
+  <si>
+    <t>季风吹过橘色的海2苦夏</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
   </si>
 </sst>
 </file>
@@ -78,7 +84,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -92,6 +98,12 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -558,137 +570,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -702,6 +714,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1227,8 +1240,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="2"/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
     <col min="3" max="3" width="11.6363636363636" style="1" customWidth="1"/>
@@ -1311,6 +1324,17 @@
         <v>7</v>
       </c>
     </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
   <si>
     <t>update_name</t>
   </si>
@@ -38,40 +38,43 @@
     <t>update_date</t>
   </si>
   <si>
-    <t>东京恐怖故事：如月车站</t>
+    <t>流芳</t>
   </si>
   <si>
     <t>剧本杀</t>
   </si>
   <si>
-    <t>2026-08-24</t>
-  </si>
-  <si>
-    <t>体温</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>【2026考研英语】石雷鹏橙啦全程班</t>
-  </si>
-  <si>
-    <t>学习资料</t>
-  </si>
-  <si>
-    <t>橙啦六级全程班[石雷鹏]</t>
-  </si>
-  <si>
-    <t>408计算机统考历年真题</t>
-  </si>
-  <si>
-    <t>1980-2025考研英语学习资料合集</t>
-  </si>
-  <si>
-    <t>季风吹过橘色的海2苦夏</t>
-  </si>
-  <si>
-    <t>2026-08-27</t>
+    <t>2026-07-26</t>
+  </si>
+  <si>
+    <t>壁上观</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>同流合屋</t>
+  </si>
+  <si>
+    <t>头颅们的失眠夜</t>
+  </si>
+  <si>
+    <t>2026-08-01</t>
+  </si>
+  <si>
+    <t>葡萄不是幸福的水果</t>
+  </si>
+  <si>
+    <t>疯兔子，白又白，砍下脑袋飞起来</t>
+  </si>
+  <si>
+    <t>2026-08-04</t>
+  </si>
+  <si>
+    <t>野狗不需要墓碑2：天生坏种</t>
+  </si>
+  <si>
+    <t>2026-08-13</t>
   </si>
 </sst>
 </file>
@@ -93,11 +96,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -707,13 +709,11 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1270,7 +1270,7 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B3" t="s">
@@ -1281,58 +1281,58 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="4" t="s">
+      <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>9</v>
+      <c r="B4" t="s">
+        <v>4</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>9</v>
+      <c r="B6" t="s">
+        <v>4</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="4" t="s">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>9</v>
+      <c r="B7" t="s">
+        <v>4</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
   <si>
     <t>update_name</t>
   </si>
@@ -38,43 +38,40 @@
     <t>update_date</t>
   </si>
   <si>
-    <t>流芳</t>
+    <t>东京恐怖故事：如月车站</t>
   </si>
   <si>
     <t>剧本杀</t>
   </si>
   <si>
-    <t>2026-07-26</t>
-  </si>
-  <si>
-    <t>壁上观</t>
-  </si>
-  <si>
-    <t>2026-07-29</t>
-  </si>
-  <si>
-    <t>同流合屋</t>
-  </si>
-  <si>
-    <t>头颅们的失眠夜</t>
-  </si>
-  <si>
-    <t>2026-08-01</t>
-  </si>
-  <si>
-    <t>葡萄不是幸福的水果</t>
-  </si>
-  <si>
-    <t>疯兔子，白又白，砍下脑袋飞起来</t>
-  </si>
-  <si>
-    <t>2026-08-04</t>
-  </si>
-  <si>
-    <t>野狗不需要墓碑2：天生坏种</t>
-  </si>
-  <si>
-    <t>2026-08-13</t>
+    <t>2026-08-24</t>
+  </si>
+  <si>
+    <t>体温</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>【2026考研英语】石雷鹏橙啦全程班</t>
+  </si>
+  <si>
+    <t>学习资料</t>
+  </si>
+  <si>
+    <t>橙啦六级全程班[石雷鹏]</t>
+  </si>
+  <si>
+    <t>408计算机统考历年真题</t>
+  </si>
+  <si>
+    <t>1980-2025考研英语学习资料合集</t>
+  </si>
+  <si>
+    <t>季风吹过橘色的海2苦夏</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
   </si>
 </sst>
 </file>
@@ -96,10 +93,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color theme="1"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -709,11 +707,13 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1270,7 +1270,7 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" t="s">
         <v>6</v>
       </c>
       <c r="B3" t="s">
@@ -1281,58 +1281,58 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" t="s">
+      <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" t="s">
-        <v>4</v>
+      <c r="B4" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
       <c r="C5" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B6" t="s">
-        <v>4</v>
+      <c r="B6" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" t="s">
+      <c r="A7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B7" t="s">
-        <v>4</v>
+      <c r="B7" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
